--- a/output/minervini_4h.xlsx
+++ b/output/minervini_4h.xlsx
@@ -1114,10 +1114,10 @@
         <v>817.5499877929688</v>
       </c>
       <c r="I9" t="n">
-        <v>262.023880250306</v>
+        <v>262.0239102537355</v>
       </c>
       <c r="J9" t="n">
-        <v>193.4083668475369</v>
+        <v>193.4083332503845</v>
       </c>
       <c r="K9" t="n">
         <v>6.341051089236993</v>
@@ -1268,10 +1268,10 @@
         <v>1982</v>
       </c>
       <c r="I11" t="n">
-        <v>821.6033372206257</v>
+        <v>821.6033975811163</v>
       </c>
       <c r="J11" t="n">
-        <v>137.8276610474978</v>
+        <v>137.8276435750843</v>
       </c>
       <c r="K11" t="n">
         <v>1.432958034800413</v>
@@ -13123,7 +13123,7 @@
         <v>3.164802535849276</v>
       </c>
       <c r="H165" t="n">
-        <v>2269.472002658311</v>
+        <v>2269.472253037084</v>
       </c>
       <c r="I165" t="n">
         <v>1353.205955540699</v>
@@ -13132,7 +13132,7 @@
         <v>57.77347056878131</v>
       </c>
       <c r="K165" t="n">
-        <v>6.298454457063762</v>
+        <v>6.298466184406726</v>
       </c>
       <c r="L165" t="n">
         <v>69.86111111111111</v>
@@ -15128,10 +15128,10 @@
         <v>2983.800048828125</v>
       </c>
       <c r="I191" t="n">
-        <v>1175.257470329055</v>
+        <v>1175.257587358084</v>
       </c>
       <c r="J191" t="n">
-        <v>108.5330330333436</v>
+        <v>108.533012268178</v>
       </c>
       <c r="K191" t="n">
         <v>21.74800021955521</v>
@@ -19283,7 +19283,7 @@
         <v>1.002257089081349</v>
       </c>
       <c r="H245" t="n">
-        <v>6552.654707500795</v>
+        <v>6552.654210942315</v>
       </c>
       <c r="I245" t="n">
         <v>4229.809203861739</v>
@@ -19292,7 +19292,7 @@
         <v>28.04360052588875</v>
       </c>
       <c r="K245" t="n">
-        <v>20.98697761264392</v>
+        <v>20.98696844428205</v>
       </c>
       <c r="L245" t="n">
         <v>50.41666666666666</v>
@@ -21824,7 +21824,7 @@
         <v>2.347184464716623</v>
       </c>
       <c r="H278" t="n">
-        <v>5038.987542214121</v>
+        <v>5038.987051168056</v>
       </c>
       <c r="I278" t="n">
         <v>3669.905008549105</v>
@@ -21833,7 +21833,7 @@
         <v>24.73074887051945</v>
       </c>
       <c r="K278" t="n">
-        <v>10.08165029413701</v>
+        <v>10.08163956675163</v>
       </c>
       <c r="L278" t="n">
         <v>51.38888888888889</v>
@@ -23136,10 +23136,10 @@
         <v>2295</v>
       </c>
       <c r="I295" t="n">
-        <v>1174.091384580817</v>
+        <v>1174.091262727543</v>
       </c>
       <c r="J295" t="n">
-        <v>67.11646140615035</v>
+        <v>67.11647875036249</v>
       </c>
       <c r="K295" t="n">
         <v>16.96651692351452</v>
@@ -23829,10 +23829,10 @@
         <v>529.9163379046904</v>
       </c>
       <c r="I304" t="n">
-        <v>387.2369934418427</v>
+        <v>387.2369630771774</v>
       </c>
       <c r="J304" t="n">
-        <v>22.84467141915105</v>
+        <v>22.84468105185065</v>
       </c>
       <c r="K304" t="n">
         <v>11.39716718654686</v>
@@ -28369,7 +28369,7 @@
         <v>-0.565653745454453</v>
       </c>
       <c r="H363" t="n">
-        <v>5875.534417311879</v>
+        <v>5875.533923201399</v>
       </c>
       <c r="I363" t="n">
         <v>5051</v>
@@ -28378,7 +28378,7 @@
         <v>8.226093842803394</v>
       </c>
       <c r="K363" t="n">
-        <v>7.482565029029153</v>
+        <v>7.482555990147244</v>
       </c>
       <c r="L363" t="n">
         <v>49.72222222222222</v>
@@ -30374,10 +30374,10 @@
         <v>443.3731066930094</v>
       </c>
       <c r="I389" t="n">
-        <v>191.8556220656042</v>
+        <v>191.8556371798532</v>
       </c>
       <c r="J389" t="n">
-        <v>82.68946003581175</v>
+        <v>82.68944564366755</v>
       </c>
       <c r="K389" t="n">
         <v>26.4973200265362</v>
@@ -32835,7 +32835,7 @@
         <v>-0.3878305876905075</v>
       </c>
       <c r="H421" t="n">
-        <v>45150.85152546577</v>
+        <v>45150.8475731383</v>
       </c>
       <c r="I421" t="n">
         <v>29525.27356749276</v>
@@ -32844,7 +32844,7 @@
         <v>23.28420909222768</v>
       </c>
       <c r="K421" t="n">
-        <v>24.04080089413674</v>
+        <v>24.04079003609423</v>
       </c>
       <c r="L421" t="n">
         <v>36.52777777777778</v>
@@ -36223,7 +36223,7 @@
         <v>0.7567775940050536</v>
       </c>
       <c r="H465" t="n">
-        <v>848.8262434052705</v>
+        <v>848.8263047717415</v>
       </c>
       <c r="I465" t="n">
         <v>495.5999980879241</v>
@@ -36232,7 +36232,7 @@
         <v>21.87247827487777</v>
       </c>
       <c r="K465" t="n">
-        <v>40.53414625915075</v>
+        <v>40.53415641916251</v>
       </c>
       <c r="L465" t="n">
         <v>37.63888888888889</v>
@@ -36842,10 +36842,10 @@
         <v>286.0804516993438</v>
       </c>
       <c r="I473" t="n">
-        <v>171.9528178807998</v>
+        <v>171.952833032562</v>
       </c>
       <c r="J473" t="n">
-        <v>22.06836531285579</v>
+        <v>22.06835455670364</v>
       </c>
       <c r="K473" t="n">
         <v>36.29369224299695</v>
@@ -37455,7 +37455,7 @@
         <v>1.157518369471844</v>
       </c>
       <c r="H481" t="n">
-        <v>329.6445669998864</v>
+        <v>329.6445362713373</v>
       </c>
       <c r="I481" t="n">
         <v>191.2413512696417</v>
@@ -37464,7 +37464,7 @@
         <v>24.28274068230316</v>
       </c>
       <c r="K481" t="n">
-        <v>38.69260230479468</v>
+        <v>38.69258937625628</v>
       </c>
       <c r="L481" t="n">
         <v>25.97222222222222</v>
@@ -38841,7 +38841,7 @@
         <v>-1.134908059779705</v>
       </c>
       <c r="H499" t="n">
-        <v>478.7148398145708</v>
+        <v>478.7148709533388</v>
       </c>
       <c r="I499" t="n">
         <v>355.1755291130353</v>
@@ -38850,7 +38850,7 @@
         <v>15.40772387109837</v>
       </c>
       <c r="K499" t="n">
-        <v>16.78820369425642</v>
+        <v>16.78821129093084</v>
       </c>
       <c r="L499" t="n">
         <v>54.72222222222223</v>
@@ -40153,10 +40153,10 @@
         <v>555.1842484654879</v>
       </c>
       <c r="I516" t="n">
-        <v>379.7398698331913</v>
+        <v>379.7399002549519</v>
       </c>
       <c r="J516" t="n">
-        <v>11.11554138162569</v>
+        <v>11.1155324799264</v>
       </c>
       <c r="K516" t="n">
         <v>31.57583419930909</v>
@@ -40997,7 +40997,7 @@
         <v>-0.6210973687980514</v>
       </c>
       <c r="H527" t="n">
-        <v>163308.4863287346</v>
+        <v>163308.5022863474</v>
       </c>
       <c r="I527" t="n">
         <v>121787.4350540836</v>
@@ -41006,7 +41006,7 @@
         <v>3.187984823058465</v>
       </c>
       <c r="K527" t="n">
-        <v>29.95025569247602</v>
+        <v>29.95026839050485</v>
       </c>
       <c r="L527" t="n">
         <v>27.91666666666667</v>
@@ -44542,10 +44542,10 @@
         <v>409.9712889887167</v>
       </c>
       <c r="I573" t="n">
-        <v>309.8384816659088</v>
+        <v>309.838511773213</v>
       </c>
       <c r="J573" t="n">
-        <v>4.457649081003479</v>
+        <v>4.457638930753949</v>
       </c>
       <c r="K573" t="n">
         <v>26.67118699833535</v>
@@ -46233,16 +46233,16 @@
         <v>-1.045338384895489</v>
       </c>
       <c r="H595" t="n">
-        <v>239.2187037807859</v>
+        <v>239.2186883393384</v>
       </c>
       <c r="I595" t="n">
-        <v>156.7443123050878</v>
+        <v>156.7442971017576</v>
       </c>
       <c r="J595" t="n">
-        <v>12.28477602264306</v>
+        <v>12.28478691364554</v>
       </c>
       <c r="K595" t="n">
-        <v>35.91971805726472</v>
+        <v>35.91970928371502</v>
       </c>
       <c r="L595" t="n">
         <v>26.52777777777778</v>
@@ -46849,7 +46849,7 @@
         <v>-1.355180243355558</v>
       </c>
       <c r="H603" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I603" t="n">
         <v>110.3499984741211</v>
@@ -46858,7 +46858,7 @@
         <v>4.630721052116682</v>
       </c>
       <c r="K603" t="n">
-        <v>35.02508395647732</v>
+        <v>35.02509926489184</v>
       </c>
       <c r="L603" t="n">
         <v>24.16666666666667</v>
@@ -48851,7 +48851,7 @@
         <v>-0.5289877462034021</v>
       </c>
       <c r="H629" t="n">
-        <v>632.5129117162858</v>
+        <v>632.5128493651639</v>
       </c>
       <c r="I629" t="n">
         <v>351.0001816860465</v>
@@ -48860,7 +48860,7 @@
         <v>19.99994136292933</v>
       </c>
       <c r="K629" t="n">
-        <v>50.16925294042692</v>
+        <v>50.16923813721701</v>
       </c>
       <c r="L629" t="n">
         <v>17.08333333333333</v>
@@ -49621,7 +49621,7 @@
         <v>-1.434342585985138</v>
       </c>
       <c r="H639" t="n">
-        <v>1608.140814494163</v>
+        <v>1608.140938678776</v>
       </c>
       <c r="I639" t="n">
         <v>1081.099975585938</v>
@@ -49630,7 +49630,7 @@
         <v>4.745171583259111</v>
       </c>
       <c r="K639" t="n">
-        <v>42.01172552307764</v>
+        <v>42.0117364895745</v>
       </c>
       <c r="L639" t="n">
         <v>15.69444444444444</v>
@@ -49698,7 +49698,7 @@
         <v>-1.666775813593147</v>
       </c>
       <c r="H640" t="n">
-        <v>154.1041584954392</v>
+        <v>154.1041427094461</v>
       </c>
       <c r="I640" t="n">
         <v>104.7068431385872</v>
@@ -49707,7 +49707,7 @@
         <v>4.176573909958581</v>
       </c>
       <c r="K640" t="n">
-        <v>41.27627054326495</v>
+        <v>41.27625607132437</v>
       </c>
       <c r="L640" t="n">
         <v>15.55555555555556</v>
@@ -49852,7 +49852,7 @@
         <v>-0.824073811416659</v>
       </c>
       <c r="H642" t="n">
-        <v>308.0746526166167</v>
+        <v>308.0746845932235</v>
       </c>
       <c r="I642" t="n">
         <v>185.2067002350832</v>
@@ -49861,7 +49861,7 @@
         <v>13.72158504516692</v>
       </c>
       <c r="K642" t="n">
-        <v>46.2703730693784</v>
+        <v>46.27038825151091</v>
       </c>
       <c r="L642" t="n">
         <v>15.27777777777778</v>
@@ -50160,7 +50160,7 @@
         <v>-0.911543638119694</v>
       </c>
       <c r="H646" t="n">
-        <v>124.8273017901132</v>
+        <v>124.8273096544699</v>
       </c>
       <c r="I646" t="n">
         <v>76.65010804466255</v>
@@ -50169,7 +50169,7 @@
         <v>7.501481247575037</v>
       </c>
       <c r="K646" t="n">
-        <v>51.48944111476668</v>
+        <v>51.48945065888879</v>
       </c>
       <c r="L646" t="n">
         <v>14.58333333333333</v>
@@ -50314,7 +50314,7 @@
         <v>-1.956888492501585</v>
       </c>
       <c r="H648" t="n">
-        <v>398.263766662724</v>
+        <v>398.2637357690495</v>
       </c>
       <c r="I648" t="n">
         <v>243.9284560598348</v>
@@ -50323,7 +50323,7 @@
         <v>9.048367827471161</v>
       </c>
       <c r="K648" t="n">
-        <v>49.72322054989626</v>
+        <v>49.7232089357329</v>
       </c>
       <c r="L648" t="n">
         <v>14.30555555555556</v>
@@ -51084,7 +51084,7 @@
         <v>-3.066272652257995</v>
       </c>
       <c r="H658" t="n">
-        <v>1255.178432949836</v>
+        <v>1255.178308316206</v>
       </c>
       <c r="I658" t="n">
         <v>855.1500244140625</v>
@@ -51093,7 +51093,7 @@
         <v>2.905919999588891</v>
       </c>
       <c r="K658" t="n">
-        <v>42.63391283520865</v>
+        <v>42.63389867229614</v>
       </c>
       <c r="L658" t="n">
         <v>11.80555555555556</v>
@@ -51546,7 +51546,7 @@
         <v>-2.188923610668525</v>
       </c>
       <c r="H664" t="n">
-        <v>729.6617501297184</v>
+        <v>729.6618113637422</v>
       </c>
       <c r="I664" t="n">
         <v>446.5</v>
@@ -51555,7 +51555,7 @@
         <v>6.830907054871216</v>
       </c>
       <c r="K664" t="n">
-        <v>52.9689203626244</v>
+        <v>52.96893319994596</v>
       </c>
       <c r="L664" t="n">
         <v>10.69444444444444</v>
@@ -51700,7 +51700,7 @@
         <v>-2.604193874278637</v>
       </c>
       <c r="H666" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I666" t="n">
         <v>163.3000030517578</v>
@@ -51709,7 +51709,7 @@
         <v>2.161664858131118</v>
       </c>
       <c r="K666" t="n">
-        <v>57.77769344677972</v>
+        <v>57.77767512531289</v>
       </c>
       <c r="L666" t="n">
         <v>10.13888888888889</v>
@@ -51777,7 +51777,7 @@
         <v>-2.148565704371641</v>
       </c>
       <c r="H667" t="n">
-        <v>406.5707642578344</v>
+        <v>406.5707952146441</v>
       </c>
       <c r="I667" t="n">
         <v>255.5</v>
@@ -51786,7 +51786,7 @@
         <v>2.661443363197158</v>
       </c>
       <c r="K667" t="n">
-        <v>55.00220479565458</v>
+        <v>55.00221659771753</v>
       </c>
       <c r="L667" t="n">
         <v>10</v>
@@ -52316,7 +52316,7 @@
         <v>-1.394065988772819</v>
       </c>
       <c r="H674" t="n">
-        <v>1211.101032727737</v>
+        <v>1211.101157071308</v>
       </c>
       <c r="I674" t="n">
         <v>577.3964738257137</v>
@@ -52325,7 +52325,7 @@
         <v>12.05471964750795</v>
       </c>
       <c r="K674" t="n">
-        <v>87.18717661943391</v>
+        <v>87.18719583791471</v>
       </c>
       <c r="L674" t="n">
         <v>8.611111111111111</v>
@@ -54010,7 +54010,7 @@
         <v>-1.677722712351626</v>
       </c>
       <c r="H696" t="n">
-        <v>891.9600709299998</v>
+        <v>891.9600088223455</v>
       </c>
       <c r="I696" t="n">
         <v>455</v>
@@ -54019,7 +54019,7 @@
         <v>1.516482175051515</v>
       </c>
       <c r="K696" t="n">
-        <v>93.10675096694101</v>
+        <v>93.1067375208152</v>
       </c>
       <c r="L696" t="n">
         <v>3.611111111111111</v>

--- a/output/minervini_4h.xlsx
+++ b/output/minervini_4h.xlsx
@@ -1576,10 +1576,10 @@
         <v>1355</v>
       </c>
       <c r="I15" t="n">
-        <v>594.6745299041222</v>
+        <v>594.6744698202933</v>
       </c>
       <c r="J15" t="n">
-        <v>123.5004037923442</v>
+        <v>123.5004263740434</v>
       </c>
       <c r="K15" t="n">
         <v>1.948688954165734</v>
@@ -1647,7 +1647,7 @@
         <v>1136.174749755859</v>
       </c>
       <c r="G16" t="n">
-        <v>10.44502439594728</v>
+        <v>10.44526596562863</v>
       </c>
       <c r="H16" t="n">
         <v>1528.699951171875</v>
@@ -4265,7 +4265,7 @@
         <v>600.9144992065429</v>
       </c>
       <c r="G50" t="n">
-        <v>5.145146325795902</v>
+        <v>5.145606272683989</v>
       </c>
       <c r="H50" t="n">
         <v>780.9500122070312</v>
@@ -4727,7 +4727,7 @@
         <v>82.51150001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>1.4899102469772</v>
+        <v>1.490659270833472</v>
       </c>
       <c r="H56" t="n">
         <v>94.5</v>
@@ -5420,16 +5420,16 @@
         <v>1758.984500732422</v>
       </c>
       <c r="G65" t="n">
-        <v>4.729884968675568</v>
+        <v>4.730789148158721</v>
       </c>
       <c r="H65" t="n">
         <v>2038.599975585938</v>
       </c>
       <c r="I65" t="n">
-        <v>1266.16157090969</v>
+        <v>1266.161452106784</v>
       </c>
       <c r="J65" t="n">
-        <v>53.61388662290467</v>
+        <v>53.61390103637152</v>
       </c>
       <c r="K65" t="n">
         <v>4.812338076397804</v>
@@ -9803,13 +9803,13 @@
         <v>10948.51</v>
       </c>
       <c r="E122" t="n">
-        <v>10198.39666666667</v>
+        <v>10198.38333333333</v>
       </c>
       <c r="F122" t="n">
-        <v>10003.755</v>
+        <v>10003.745</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3675333577970896</v>
+        <v>0.3675337265431899</v>
       </c>
       <c r="H122" t="n">
         <v>12724.74699012829</v>
@@ -10194,7 +10194,7 @@
         <v>662.3535003662109</v>
       </c>
       <c r="G127" t="n">
-        <v>4.428470598264478</v>
+        <v>4.427647380790867</v>
       </c>
       <c r="H127" t="n">
         <v>823</v>
@@ -13508,7 +13508,7 @@
         <v>2.618231883114275</v>
       </c>
       <c r="H170" t="n">
-        <v>2256.187906504501</v>
+        <v>2256.187656125729</v>
       </c>
       <c r="I170" t="n">
         <v>1345.285007075603</v>
@@ -13517,7 +13517,7 @@
         <v>51.26162959606255</v>
       </c>
       <c r="K170" t="n">
-        <v>10.87463164949134</v>
+        <v>10.87461934526166</v>
       </c>
       <c r="L170" t="n">
         <v>62.91666666666666</v>
@@ -15963,13 +15963,13 @@
         <v>608.205</v>
       </c>
       <c r="E202" t="n">
-        <v>618.5556673177083</v>
+        <v>618.5560005696615</v>
       </c>
       <c r="F202" t="n">
-        <v>598.8162496948243</v>
+        <v>598.816499633789</v>
       </c>
       <c r="G202" t="n">
-        <v>2.846537311976882</v>
+        <v>2.846536090045637</v>
       </c>
       <c r="H202" t="n">
         <v>703.5025243881884</v>
@@ -16046,7 +16046,7 @@
         <v>1176.859999389648</v>
       </c>
       <c r="G203" t="n">
-        <v>0.7447824157451599</v>
+        <v>0.7445237000404559</v>
       </c>
       <c r="H203" t="n">
         <v>1278.952852189353</v>
@@ -16665,7 +16665,7 @@
         <v>3.989739780862767</v>
       </c>
       <c r="H211" t="n">
-        <v>1409.944189808421</v>
+        <v>1409.944064008135</v>
       </c>
       <c r="I211" t="n">
         <v>905.5050975494345</v>
@@ -16674,7 +16674,7 @@
         <v>38.57459800325655</v>
       </c>
       <c r="K211" t="n">
-        <v>12.3640528325758</v>
+        <v>12.36404280705134</v>
       </c>
       <c r="L211" t="n">
         <v>58.75</v>
@@ -16822,10 +16822,10 @@
         <v>489.5369231157038</v>
       </c>
       <c r="I213" t="n">
-        <v>331.4688100886702</v>
+        <v>331.4688402352409</v>
       </c>
       <c r="J213" t="n">
-        <v>27.41772174297006</v>
+        <v>27.41771015452827</v>
       </c>
       <c r="K213" t="n">
         <v>15.90787641559095</v>
@@ -17432,7 +17432,7 @@
         <v>1643.566498413086</v>
       </c>
       <c r="G221" t="n">
-        <v>2.436116909713126</v>
+        <v>2.435701949878011</v>
       </c>
       <c r="H221" t="n">
         <v>2090.02010392206</v>
@@ -17823,10 +17823,10 @@
         <v>2295</v>
       </c>
       <c r="I226" t="n">
-        <v>1174.091262727543</v>
+        <v>1174.091384580817</v>
       </c>
       <c r="J226" t="n">
-        <v>71.0258873177537</v>
+        <v>71.02586956780297</v>
       </c>
       <c r="K226" t="n">
         <v>14.29282868525896</v>
@@ -18051,16 +18051,16 @@
         <v>-0.3587029685777399</v>
       </c>
       <c r="H229" t="n">
-        <v>1766.733060850261</v>
+        <v>1766.733188761222</v>
       </c>
       <c r="I229" t="n">
-        <v>941.3309959266335</v>
+        <v>941.3310566553616</v>
       </c>
       <c r="J229" t="n">
-        <v>59.34883760238028</v>
+        <v>59.34882732220075</v>
       </c>
       <c r="K229" t="n">
-        <v>17.78220405668405</v>
+        <v>17.78221258408148</v>
       </c>
       <c r="L229" t="n">
         <v>81.38888888888889</v>
@@ -19588,7 +19588,7 @@
         <v>462.0267495727539</v>
       </c>
       <c r="G249" t="n">
-        <v>4.634745201952084</v>
+        <v>4.634152792100976</v>
       </c>
       <c r="H249" t="n">
         <v>715.4154766283395</v>
@@ -19668,7 +19668,7 @@
         <v>1.593924005927727</v>
       </c>
       <c r="H250" t="n">
-        <v>5005.771680286142</v>
+        <v>5005.771184298104</v>
       </c>
       <c r="I250" t="n">
         <v>3669.905008549105</v>
@@ -19677,7 +19677,7 @@
         <v>23.16395082353859</v>
       </c>
       <c r="K250" t="n">
-        <v>10.74716106827749</v>
+        <v>10.7471500950908</v>
       </c>
       <c r="L250" t="n">
         <v>58.47222222222223</v>
@@ -20204,7 +20204,7 @@
         <v>623.223249206543</v>
       </c>
       <c r="G257" t="n">
-        <v>3.729857914627099</v>
+        <v>3.730591656742899</v>
       </c>
       <c r="H257" t="n">
         <v>878.5999755859375</v>
@@ -25363,7 +25363,7 @@
         <v>177.2640493774414</v>
       </c>
       <c r="G324" t="n">
-        <v>3.264892763127092</v>
+        <v>3.267238927983351</v>
       </c>
       <c r="H324" t="n">
         <v>242.6000061035156</v>
@@ -26367,7 +26367,7 @@
         <v>-1.212347602710029</v>
       </c>
       <c r="H337" t="n">
-        <v>1117.559301306357</v>
+        <v>1117.559425954049</v>
       </c>
       <c r="I337" t="n">
         <v>612.1496526863262</v>
@@ -26376,7 +26376,7 @@
         <v>31.66714976688965</v>
       </c>
       <c r="K337" t="n">
-        <v>38.65500016207899</v>
+        <v>38.65501562705325</v>
       </c>
       <c r="L337" t="n">
         <v>50.83333333333333</v>
@@ -27987,10 +27987,10 @@
         <v>359.3387168134344</v>
       </c>
       <c r="I358" t="n">
-        <v>206.1211021779015</v>
+        <v>206.1210871445057</v>
       </c>
       <c r="J358" t="n">
-        <v>39.72368523016601</v>
+        <v>39.72369542088208</v>
       </c>
       <c r="K358" t="n">
         <v>24.77038778244252</v>
@@ -28064,10 +28064,10 @@
         <v>1093.53919041171</v>
       </c>
       <c r="I359" t="n">
-        <v>491.2850236715819</v>
+        <v>491.2850813456647</v>
       </c>
       <c r="J359" t="n">
-        <v>40.45817693279794</v>
+        <v>40.45816044380442</v>
       </c>
       <c r="K359" t="n">
         <v>58.47245993138077</v>
@@ -29367,7 +29367,7 @@
         <v>2638.381005859375</v>
       </c>
       <c r="G376" t="n">
-        <v>0.06456996707027152</v>
+        <v>0.06371607699273696</v>
       </c>
       <c r="H376" t="n">
         <v>2960.01877635178</v>
@@ -30294,7 +30294,7 @@
         <v>0.8953425519043989</v>
       </c>
       <c r="H388" t="n">
-        <v>390.5481555478003</v>
+        <v>390.5481869352945</v>
       </c>
       <c r="I388" t="n">
         <v>203.5784807586748</v>
@@ -30303,7 +30303,7 @@
         <v>37.53909497532626</v>
       </c>
       <c r="K388" t="n">
-        <v>39.4814841242144</v>
+        <v>39.48149533403375</v>
       </c>
       <c r="L388" t="n">
         <v>38.47222222222222</v>
@@ -32992,10 +32992,10 @@
         <v>385.3928663983843</v>
       </c>
       <c r="I423" t="n">
-        <v>282.670901059285</v>
+        <v>282.6708709611926</v>
       </c>
       <c r="J423" t="n">
-        <v>16.74353418174748</v>
+        <v>16.74354661230912</v>
       </c>
       <c r="K423" t="n">
         <v>16.7857170904195</v>
@@ -33146,10 +33146,10 @@
         <v>2765.379504159864</v>
       </c>
       <c r="I425" t="n">
-        <v>1963.170239604111</v>
+        <v>1963.170361427068</v>
       </c>
       <c r="J425" t="n">
-        <v>11.31485210721246</v>
+        <v>11.31484519965893</v>
       </c>
       <c r="K425" t="n">
         <v>26.54461366267797</v>
@@ -33220,7 +33220,7 @@
         <v>-0.6726330655565382</v>
       </c>
       <c r="H426" t="n">
-        <v>5875.533923201399</v>
+        <v>5875.534417311879</v>
       </c>
       <c r="I426" t="n">
         <v>5051</v>
@@ -33229,7 +33229,7 @@
         <v>4.414967333201347</v>
       </c>
       <c r="K426" t="n">
-        <v>11.40564890408418</v>
+        <v>11.40565827288356</v>
       </c>
       <c r="L426" t="n">
         <v>42.22222222222222</v>
@@ -33756,7 +33756,7 @@
         <v>1237.708001098633</v>
       </c>
       <c r="G433" t="n">
-        <v>-1.315728634439939</v>
+        <v>-1.314902471774571</v>
       </c>
       <c r="H433" t="n">
         <v>1405.983809538553</v>
@@ -37920,10 +37920,10 @@
         <v>555.1842484654879</v>
       </c>
       <c r="I487" t="n">
-        <v>379.7398698331913</v>
+        <v>379.7399002549519</v>
       </c>
       <c r="J487" t="n">
-        <v>14.4994303558285</v>
+        <v>14.49942118303877</v>
       </c>
       <c r="K487" t="n">
         <v>27.68727324110241</v>
@@ -38225,7 +38225,7 @@
         <v>-0.539875012389901</v>
       </c>
       <c r="H491" t="n">
-        <v>286.0804516993438</v>
+        <v>286.0804190389319</v>
       </c>
       <c r="I491" t="n">
         <v>171.9528178807998</v>
@@ -38234,7 +38234,7 @@
         <v>20.0212985319485</v>
       </c>
       <c r="K491" t="n">
-        <v>38.61829873576517</v>
+        <v>38.61828291038911</v>
       </c>
       <c r="L491" t="n">
         <v>34.86111111111111</v>
@@ -38992,7 +38992,7 @@
         <v>2666.793994140625</v>
       </c>
       <c r="G501" t="n">
-        <v>0.2038424130119676</v>
+        <v>0.2023175885779827</v>
       </c>
       <c r="H501" t="n">
         <v>3198.009229338596</v>
@@ -39146,10 +39146,10 @@
         <v>638.7837503051758</v>
       </c>
       <c r="G503" t="n">
-        <v>-0.01991666379936863</v>
+        <v>-0.02191180008949134</v>
       </c>
       <c r="H503" t="n">
-        <v>848.8263661382125</v>
+        <v>848.8262434052705</v>
       </c>
       <c r="I503" t="n">
         <v>495.5999980879241</v>
@@ -39158,7 +39158,7 @@
         <v>21.03510449964094</v>
       </c>
       <c r="K503" t="n">
-        <v>41.50644339179528</v>
+        <v>41.50642293118896</v>
       </c>
       <c r="L503" t="n">
         <v>30</v>
@@ -39377,7 +39377,7 @@
         <v>4962.071003417968</v>
       </c>
       <c r="G506" t="n">
-        <v>-1.609149187569381</v>
+        <v>-1.609627158821836</v>
       </c>
       <c r="H506" t="n">
         <v>7036</v>
@@ -39457,7 +39457,7 @@
         <v>-1.750802824373099</v>
       </c>
       <c r="H507" t="n">
-        <v>308.0746526166167</v>
+        <v>308.0746845932235</v>
       </c>
       <c r="I507" t="n">
         <v>185.2067002350832</v>
@@ -39466,7 +39466,7 @@
         <v>22.80873027786765</v>
       </c>
       <c r="K507" t="n">
-        <v>35.44720015394032</v>
+        <v>35.44721421268164</v>
       </c>
       <c r="L507" t="n">
         <v>28.88888888888889</v>
@@ -39765,7 +39765,7 @@
         <v>-0.7578020093248039</v>
       </c>
       <c r="H511" t="n">
-        <v>260.4933484681973</v>
+        <v>260.4933650598492</v>
       </c>
       <c r="I511" t="n">
         <v>171.6534204603822</v>
@@ -39774,7 +39774,7 @@
         <v>16.11187066592401</v>
       </c>
       <c r="K511" t="n">
-        <v>30.69758248911556</v>
+        <v>30.6975908136613</v>
       </c>
       <c r="L511" t="n">
         <v>26.94444444444444</v>
@@ -40458,7 +40458,7 @@
         <v>-0.9656489452365413</v>
       </c>
       <c r="H520" t="n">
-        <v>163308.4863287346</v>
+        <v>163308.5022863474</v>
       </c>
       <c r="I520" t="n">
         <v>121787.4350540836</v>
@@ -40467,7 +40467,7 @@
         <v>1.845481797788318</v>
       </c>
       <c r="K520" t="n">
-        <v>31.66322919235265</v>
+        <v>31.6632420577639</v>
       </c>
       <c r="L520" t="n">
         <v>24.72222222222222</v>
@@ -41225,7 +41225,7 @@
         <v>548.0342497253419</v>
       </c>
       <c r="G530" t="n">
-        <v>-0.5777648461229634</v>
+        <v>-0.5779452247440475</v>
       </c>
       <c r="H530" t="n">
         <v>721</v>
@@ -42457,7 +42457,7 @@
         <v>1198.636000366211</v>
       </c>
       <c r="G546" t="n">
-        <v>-2.139221734541186</v>
+        <v>-2.138702382328195</v>
       </c>
       <c r="H546" t="n">
         <v>1546.338945569448</v>
@@ -42534,7 +42534,7 @@
         <v>2248.912498168945</v>
       </c>
       <c r="G547" t="n">
-        <v>-2.217390551970833</v>
+        <v>-2.216880380078623</v>
       </c>
       <c r="H547" t="n">
         <v>3287.161392369851</v>
@@ -42845,7 +42845,7 @@
         <v>-4.82935555707863</v>
       </c>
       <c r="H551" t="n">
-        <v>758.5896367271307</v>
+        <v>758.589574672296</v>
       </c>
       <c r="I551" t="n">
         <v>400.6499938964844</v>
@@ -42854,7 +42854,7 @@
         <v>17.12217824749045</v>
       </c>
       <c r="K551" t="n">
-        <v>61.66001848207367</v>
+        <v>61.66000525781481</v>
       </c>
       <c r="L551" t="n">
         <v>13.19444444444444</v>
@@ -43307,7 +43307,7 @@
         <v>-2.106398644123408</v>
       </c>
       <c r="H557" t="n">
-        <v>1181.515511428121</v>
+        <v>1181.515387363553</v>
       </c>
       <c r="I557" t="n">
         <v>577.3964738257137</v>
@@ -43316,7 +43316,7 @@
         <v>8.989232930944802</v>
       </c>
       <c r="K557" t="n">
-        <v>87.75076026488394</v>
+        <v>87.75074055018976</v>
       </c>
       <c r="L557" t="n">
         <v>8.888888888888889</v>
@@ -43458,7 +43458,7 @@
         <v>194.3287507629394</v>
       </c>
       <c r="G559" t="n">
-        <v>-3.727183490370556</v>
+        <v>-3.726062648509398</v>
       </c>
       <c r="H559" t="n">
         <v>322.394908081455</v>
@@ -43615,16 +43615,16 @@
         <v>-0.8873826761097159</v>
       </c>
       <c r="H561" t="n">
-        <v>828.2152668923007</v>
+        <v>828.2152046613147</v>
       </c>
       <c r="I561" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J561" t="n">
-        <v>14.00651352578135</v>
+        <v>14.0065219917685</v>
       </c>
       <c r="K561" t="n">
-        <v>78.88018723375826</v>
+        <v>78.88017379294054</v>
       </c>
       <c r="L561" t="n">
         <v>6.805555555555555</v>
@@ -44773,10 +44773,10 @@
         <v>409.9712889887167</v>
       </c>
       <c r="I576" t="n">
-        <v>309.8384816659088</v>
+        <v>309.838511773213</v>
       </c>
       <c r="J576" t="n">
-        <v>5.409761998408036</v>
+        <v>5.409751755640779</v>
       </c>
       <c r="K576" t="n">
         <v>25.52703041247848</v>
@@ -45543,10 +45543,10 @@
         <v>962.6932158005569</v>
       </c>
       <c r="I586" t="n">
-        <v>726.0614279588375</v>
+        <v>726.0613673587077</v>
       </c>
       <c r="J586" t="n">
-        <v>3.744665532997282</v>
+        <v>3.744674191962605</v>
       </c>
       <c r="K586" t="n">
         <v>27.80527259217482</v>
@@ -47083,10 +47083,10 @@
         <v>476.8288845013619</v>
       </c>
       <c r="I606" t="n">
-        <v>317.6634042148347</v>
+        <v>317.6633741663369</v>
       </c>
       <c r="J606" t="n">
-        <v>6.401932207278027</v>
+        <v>6.40194227207771</v>
       </c>
       <c r="K606" t="n">
         <v>41.07363446785855</v>
@@ -47465,7 +47465,7 @@
         <v>-1.197001023375388</v>
       </c>
       <c r="H611" t="n">
-        <v>523.4329909937741</v>
+        <v>523.4329289989834</v>
       </c>
       <c r="I611" t="n">
         <v>394.4382907843191</v>
@@ -47474,7 +47474,7 @@
         <v>5.960811100758079</v>
       </c>
       <c r="K611" t="n">
-        <v>25.23818057325284</v>
+        <v>25.23816574018933</v>
       </c>
       <c r="L611" t="n">
         <v>24.44444444444444</v>
@@ -48235,16 +48235,16 @@
         <v>-2.342743021714566</v>
       </c>
       <c r="H621" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2186883393384</v>
       </c>
       <c r="I621" t="n">
-        <v>156.7442971017576</v>
+        <v>156.7443123050878</v>
       </c>
       <c r="J621" t="n">
-        <v>10.78552592171929</v>
+        <v>10.78551517613684</v>
       </c>
       <c r="K621" t="n">
-        <v>37.75910239334252</v>
+        <v>37.75911128562471</v>
       </c>
       <c r="L621" t="n">
         <v>21.25</v>
@@ -48694,7 +48694,7 @@
         <v>229.043649520874</v>
       </c>
       <c r="G627" t="n">
-        <v>-2.329384130519763</v>
+        <v>-2.329675674747778</v>
       </c>
       <c r="H627" t="n">
         <v>285.8408427878384</v>
@@ -49852,7 +49852,7 @@
         <v>-2.443351866282273</v>
       </c>
       <c r="H642" t="n">
-        <v>154.1041584954392</v>
+        <v>154.1041427094461</v>
       </c>
       <c r="I642" t="n">
         <v>104.7068431385872</v>
@@ -49861,7 +49861,7 @@
         <v>3.699050201848864</v>
       </c>
       <c r="K642" t="n">
-        <v>41.92683357587146</v>
+        <v>41.92681903728905</v>
       </c>
       <c r="L642" t="n">
         <v>15.13888888888889</v>
@@ -51546,7 +51546,7 @@
         <v>-3.186612091689878</v>
       </c>
       <c r="H664" t="n">
-        <v>396.5816333492734</v>
+        <v>396.5816020628056</v>
       </c>
       <c r="I664" t="n">
         <v>243.9284560598348</v>
@@ -51555,7 +51555,7 @@
         <v>6.650121145632348</v>
       </c>
       <c r="K664" t="n">
-        <v>52.44345287475816</v>
+        <v>52.4434408484393</v>
       </c>
       <c r="L664" t="n">
         <v>10.55555555555556</v>
@@ -51777,7 +51777,7 @@
         <v>-1.259978388112681</v>
       </c>
       <c r="H667" t="n">
-        <v>3469.395895156339</v>
+        <v>3469.396141243416</v>
       </c>
       <c r="I667" t="n">
         <v>1805.687062514093</v>
@@ -51786,7 +51786,7 @@
         <v>9.121899653566556</v>
       </c>
       <c r="K667" t="n">
-        <v>76.07571316327164</v>
+        <v>76.07572565246539</v>
       </c>
       <c r="L667" t="n">
         <v>10</v>
@@ -54700,7 +54700,7 @@
         <v>776.7295007324219</v>
       </c>
       <c r="G705" t="n">
-        <v>-4.006705721180515</v>
+        <v>-4.007803065774351</v>
       </c>
       <c r="H705" t="n">
         <v>1235.294421692934</v>

--- a/output/minervini_4h.xlsx
+++ b/output/minervini_4h.xlsx
@@ -1576,10 +1576,10 @@
         <v>1355</v>
       </c>
       <c r="I15" t="n">
-        <v>594.6744698202933</v>
+        <v>594.6745299041222</v>
       </c>
       <c r="J15" t="n">
-        <v>123.5004263740434</v>
+        <v>123.5004037923442</v>
       </c>
       <c r="K15" t="n">
         <v>1.948688954165734</v>
@@ -1647,7 +1647,7 @@
         <v>1136.174749755859</v>
       </c>
       <c r="G16" t="n">
-        <v>10.44526596562863</v>
+        <v>10.44502439594728</v>
       </c>
       <c r="H16" t="n">
         <v>1528.699951171875</v>
@@ -1730,10 +1730,10 @@
         <v>844</v>
       </c>
       <c r="I17" t="n">
-        <v>399.8349725758499</v>
+        <v>399.8350028638013</v>
       </c>
       <c r="J17" t="n">
-        <v>106.2100757941053</v>
+        <v>106.21006017346</v>
       </c>
       <c r="K17" t="n">
         <v>2.365069739235892</v>
@@ -4265,7 +4265,7 @@
         <v>600.9144992065429</v>
       </c>
       <c r="G50" t="n">
-        <v>5.145606272683989</v>
+        <v>5.145146325795902</v>
       </c>
       <c r="H50" t="n">
         <v>780.9500122070312</v>
@@ -4727,7 +4727,7 @@
         <v>82.51150001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>1.490659270833472</v>
+        <v>1.4899102469772</v>
       </c>
       <c r="H56" t="n">
         <v>94.5</v>
@@ -5420,7 +5420,7 @@
         <v>1758.984500732422</v>
       </c>
       <c r="G65" t="n">
-        <v>4.730789148158721</v>
+        <v>4.729884968675568</v>
       </c>
       <c r="H65" t="n">
         <v>2038.599975585938</v>
@@ -7274,10 +7274,10 @@
         <v>2983.800048828125</v>
       </c>
       <c r="I89" t="n">
-        <v>1175.257587358084</v>
+        <v>1175.257470329055</v>
       </c>
       <c r="J89" t="n">
-        <v>115.1017808515331</v>
+        <v>115.1018022707993</v>
       </c>
       <c r="K89" t="n">
         <v>18.03006522263153</v>
@@ -9803,13 +9803,13 @@
         <v>10948.51</v>
       </c>
       <c r="E122" t="n">
-        <v>10198.38333333333</v>
+        <v>10198.39666666667</v>
       </c>
       <c r="F122" t="n">
-        <v>10003.745</v>
+        <v>10003.755</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3675337265431899</v>
+        <v>0.3675333577970896</v>
       </c>
       <c r="H122" t="n">
         <v>12724.74699012829</v>
@@ -10194,7 +10194,7 @@
         <v>662.3535003662109</v>
       </c>
       <c r="G127" t="n">
-        <v>4.427647380790867</v>
+        <v>4.428470598264478</v>
       </c>
       <c r="H127" t="n">
         <v>823</v>
@@ -15963,13 +15963,13 @@
         <v>608.205</v>
       </c>
       <c r="E202" t="n">
-        <v>618.5560005696615</v>
+        <v>618.5556673177083</v>
       </c>
       <c r="F202" t="n">
-        <v>598.816499633789</v>
+        <v>598.8162496948243</v>
       </c>
       <c r="G202" t="n">
-        <v>2.846536090045637</v>
+        <v>2.846537311976882</v>
       </c>
       <c r="H202" t="n">
         <v>703.5025243881884</v>
@@ -16046,10 +16046,10 @@
         <v>1176.859999389648</v>
       </c>
       <c r="G203" t="n">
-        <v>0.7445237000404559</v>
+        <v>0.7447824157451599</v>
       </c>
       <c r="H203" t="n">
-        <v>1278.952852189353</v>
+        <v>1278.952725191461</v>
       </c>
       <c r="I203" t="n">
         <v>865.2617122743181</v>
@@ -16058,7 +16058,7 @@
         <v>40.77821291597348</v>
       </c>
       <c r="K203" t="n">
-        <v>4.995721026440703</v>
+        <v>4.995710600540115</v>
       </c>
       <c r="L203" t="n">
         <v>65.97222222222221</v>
@@ -16822,10 +16822,10 @@
         <v>489.5369231157038</v>
       </c>
       <c r="I213" t="n">
-        <v>331.4688402352409</v>
+        <v>331.4688100886702</v>
       </c>
       <c r="J213" t="n">
-        <v>27.41771015452827</v>
+        <v>27.41772174297006</v>
       </c>
       <c r="K213" t="n">
         <v>15.90787641559095</v>
@@ -17432,7 +17432,7 @@
         <v>1643.566498413086</v>
       </c>
       <c r="G221" t="n">
-        <v>2.435701949878011</v>
+        <v>2.436116909713126</v>
       </c>
       <c r="H221" t="n">
         <v>2090.02010392206</v>
@@ -17823,10 +17823,10 @@
         <v>2295</v>
       </c>
       <c r="I226" t="n">
-        <v>1174.091384580817</v>
+        <v>1174.091262727543</v>
       </c>
       <c r="J226" t="n">
-        <v>71.02586956780297</v>
+        <v>71.0258873177537</v>
       </c>
       <c r="K226" t="n">
         <v>14.29282868525896</v>
@@ -19588,7 +19588,7 @@
         <v>462.0267495727539</v>
       </c>
       <c r="G249" t="n">
-        <v>4.634152792100976</v>
+        <v>4.634745201952084</v>
       </c>
       <c r="H249" t="n">
         <v>715.4154766283395</v>
@@ -19668,7 +19668,7 @@
         <v>1.593924005927727</v>
       </c>
       <c r="H250" t="n">
-        <v>5005.771184298104</v>
+        <v>5005.771680286142</v>
       </c>
       <c r="I250" t="n">
         <v>3669.905008549105</v>
@@ -19677,7 +19677,7 @@
         <v>23.16395082353859</v>
       </c>
       <c r="K250" t="n">
-        <v>10.7471500950908</v>
+        <v>10.74716106827749</v>
       </c>
       <c r="L250" t="n">
         <v>58.47222222222223</v>
@@ -20204,7 +20204,7 @@
         <v>623.223249206543</v>
       </c>
       <c r="G257" t="n">
-        <v>3.730591656742899</v>
+        <v>3.729857914627099</v>
       </c>
       <c r="H257" t="n">
         <v>878.5999755859375</v>
@@ -25363,7 +25363,7 @@
         <v>177.2640493774414</v>
       </c>
       <c r="G324" t="n">
-        <v>3.267238927983351</v>
+        <v>3.264892763127092</v>
       </c>
       <c r="H324" t="n">
         <v>242.6000061035156</v>
@@ -26367,7 +26367,7 @@
         <v>-1.212347602710029</v>
       </c>
       <c r="H337" t="n">
-        <v>1117.559425954049</v>
+        <v>1117.559301306357</v>
       </c>
       <c r="I337" t="n">
         <v>612.1496526863262</v>
@@ -26376,7 +26376,7 @@
         <v>31.66714976688965</v>
       </c>
       <c r="K337" t="n">
-        <v>38.65501562705325</v>
+        <v>38.65500016207899</v>
       </c>
       <c r="L337" t="n">
         <v>50.83333333333333</v>
@@ -27910,10 +27910,10 @@
         <v>755.9652099609375</v>
       </c>
       <c r="I357" t="n">
-        <v>306.8420198526935</v>
+        <v>306.8419898026673</v>
       </c>
       <c r="J357" t="n">
-        <v>61.48374992378034</v>
+        <v>61.48376573840506</v>
       </c>
       <c r="K357" t="n">
         <v>52.5661372272326</v>
@@ -28064,10 +28064,10 @@
         <v>1093.53919041171</v>
       </c>
       <c r="I359" t="n">
-        <v>491.2850813456647</v>
+        <v>491.2850236715819</v>
       </c>
       <c r="J359" t="n">
-        <v>40.45816044380442</v>
+        <v>40.45817693279794</v>
       </c>
       <c r="K359" t="n">
         <v>58.47245993138077</v>
@@ -29367,7 +29367,7 @@
         <v>2638.381005859375</v>
       </c>
       <c r="G376" t="n">
-        <v>0.06371607699273696</v>
+        <v>0.06456996707027152</v>
       </c>
       <c r="H376" t="n">
         <v>2960.01877635178</v>
@@ -30294,7 +30294,7 @@
         <v>0.8953425519043989</v>
       </c>
       <c r="H388" t="n">
-        <v>390.5481869352945</v>
+        <v>390.5481555478003</v>
       </c>
       <c r="I388" t="n">
         <v>203.5784807586748</v>
@@ -30303,7 +30303,7 @@
         <v>37.53909497532626</v>
       </c>
       <c r="K388" t="n">
-        <v>39.48149533403375</v>
+        <v>39.4814841242144</v>
       </c>
       <c r="L388" t="n">
         <v>38.47222222222222</v>
@@ -32992,10 +32992,10 @@
         <v>385.3928663983843</v>
       </c>
       <c r="I423" t="n">
-        <v>282.6708709611926</v>
+        <v>282.670901059285</v>
       </c>
       <c r="J423" t="n">
-        <v>16.74354661230912</v>
+        <v>16.74353418174748</v>
       </c>
       <c r="K423" t="n">
         <v>16.7857170904195</v>
@@ -33146,10 +33146,10 @@
         <v>2765.379504159864</v>
       </c>
       <c r="I425" t="n">
-        <v>1963.170361427068</v>
+        <v>1963.170239604111</v>
       </c>
       <c r="J425" t="n">
-        <v>11.31484519965893</v>
+        <v>11.31485210721246</v>
       </c>
       <c r="K425" t="n">
         <v>26.54461366267797</v>
@@ -33451,7 +33451,7 @@
         <v>-0.5717703669805174</v>
       </c>
       <c r="H429" t="n">
-        <v>1300.436795781491</v>
+        <v>1300.436668328248</v>
       </c>
       <c r="I429" t="n">
         <v>885.652283987356</v>
@@ -33460,7 +33460,7 @@
         <v>21.26655341130843</v>
       </c>
       <c r="K429" t="n">
-        <v>21.08350053831389</v>
+        <v>21.08348867115899</v>
       </c>
       <c r="L429" t="n">
         <v>40.97222222222222</v>
@@ -33756,7 +33756,7 @@
         <v>1237.708001098633</v>
       </c>
       <c r="G433" t="n">
-        <v>-1.314902471774571</v>
+        <v>-1.315728634439939</v>
       </c>
       <c r="H433" t="n">
         <v>1405.983809538553</v>
@@ -34452,7 +34452,7 @@
         <v>-1.370414881390603</v>
       </c>
       <c r="H442" t="n">
-        <v>623.6463522815318</v>
+        <v>623.6462906209067</v>
       </c>
       <c r="I442" t="n">
         <v>351.0001816860465</v>
@@ -34461,7 +34461,7 @@
         <v>30.55548797689327</v>
       </c>
       <c r="K442" t="n">
-        <v>36.0930392321946</v>
+        <v>36.09302577652083</v>
       </c>
       <c r="L442" t="n">
         <v>32.77777777777778</v>
@@ -35838,7 +35838,7 @@
         <v>-5.784913128577573</v>
       </c>
       <c r="H460" t="n">
-        <v>541.0236304500187</v>
+        <v>541.0235690240457</v>
       </c>
       <c r="I460" t="n">
         <v>271.5615990811692</v>
@@ -35847,7 +35847,7 @@
         <v>25.10973611495398</v>
       </c>
       <c r="K460" t="n">
-        <v>59.24168666667218</v>
+        <v>59.24166858691559</v>
       </c>
       <c r="L460" t="n">
         <v>13.61111111111111</v>
@@ -37920,10 +37920,10 @@
         <v>555.1842484654879</v>
       </c>
       <c r="I487" t="n">
-        <v>379.7399002549519</v>
+        <v>379.7398698331913</v>
       </c>
       <c r="J487" t="n">
-        <v>14.49942118303877</v>
+        <v>14.4994303558285</v>
       </c>
       <c r="K487" t="n">
         <v>27.68727324110241</v>
@@ -38992,7 +38992,7 @@
         <v>2666.793994140625</v>
       </c>
       <c r="G501" t="n">
-        <v>0.2023175885779827</v>
+        <v>0.2038424130119676</v>
       </c>
       <c r="H501" t="n">
         <v>3198.009229338596</v>
@@ -39146,10 +39146,10 @@
         <v>638.7837503051758</v>
       </c>
       <c r="G503" t="n">
-        <v>-0.02191180008949134</v>
+        <v>-0.01991666379936863</v>
       </c>
       <c r="H503" t="n">
-        <v>848.8262434052705</v>
+        <v>848.8263047717415</v>
       </c>
       <c r="I503" t="n">
         <v>495.5999980879241</v>
@@ -39158,7 +39158,7 @@
         <v>21.03510449964094</v>
       </c>
       <c r="K503" t="n">
-        <v>41.50642293118896</v>
+        <v>41.50643316149214</v>
       </c>
       <c r="L503" t="n">
         <v>30</v>
@@ -39377,7 +39377,7 @@
         <v>4962.071003417968</v>
       </c>
       <c r="G506" t="n">
-        <v>-1.609627158821836</v>
+        <v>-1.609149187569381</v>
       </c>
       <c r="H506" t="n">
         <v>7036</v>
@@ -39765,16 +39765,16 @@
         <v>-0.7578020093248039</v>
       </c>
       <c r="H511" t="n">
-        <v>260.4933650598492</v>
+        <v>260.4933318765453</v>
       </c>
       <c r="I511" t="n">
-        <v>171.6534204603822</v>
+        <v>171.6534052563282</v>
       </c>
       <c r="J511" t="n">
-        <v>16.11187066592401</v>
+        <v>16.11188095043396</v>
       </c>
       <c r="K511" t="n">
-        <v>30.6975908136613</v>
+        <v>30.6975741645698</v>
       </c>
       <c r="L511" t="n">
         <v>26.94444444444444</v>
@@ -40535,7 +40535,7 @@
         <v>-0.6460711842523614</v>
       </c>
       <c r="H521" t="n">
-        <v>533.7088183031568</v>
+        <v>533.7087547028075</v>
       </c>
       <c r="I521" t="n">
         <v>363.2227809620478</v>
@@ -40544,7 +40544,7 @@
         <v>10.15278420692478</v>
       </c>
       <c r="K521" t="n">
-        <v>33.39385407684132</v>
+        <v>33.39383818072825</v>
       </c>
       <c r="L521" t="n">
         <v>24.58333333333333</v>
@@ -41225,7 +41225,7 @@
         <v>548.0342497253419</v>
       </c>
       <c r="G530" t="n">
-        <v>-0.5779452247440475</v>
+        <v>-0.5777648461229634</v>
       </c>
       <c r="H530" t="n">
         <v>721</v>
@@ -42457,10 +42457,10 @@
         <v>1198.636000366211</v>
       </c>
       <c r="G546" t="n">
-        <v>-2.138702382328195</v>
+        <v>-2.139221734541186</v>
       </c>
       <c r="H546" t="n">
-        <v>1546.338945569448</v>
+        <v>1546.339069162078</v>
       </c>
       <c r="I546" t="n">
         <v>1081.099975585938</v>
@@ -42469,7 +42469,7 @@
         <v>1.424477362115928</v>
       </c>
       <c r="K546" t="n">
-        <v>41.02498363606457</v>
+        <v>41.02499490762222</v>
       </c>
       <c r="L546" t="n">
         <v>15.69444444444444</v>
@@ -42534,10 +42534,10 @@
         <v>2248.912498168945</v>
       </c>
       <c r="G547" t="n">
-        <v>-2.216880380078623</v>
+        <v>-2.217390551970833</v>
       </c>
       <c r="H547" t="n">
-        <v>3287.161392369851</v>
+        <v>3287.161645949698</v>
       </c>
       <c r="I547" t="n">
         <v>1966.020518717901</v>
@@ -42546,7 +42546,7 @@
         <v>5.899199941093825</v>
       </c>
       <c r="K547" t="n">
-        <v>57.88479310133767</v>
+        <v>57.88480528096531</v>
       </c>
       <c r="L547" t="n">
         <v>15.55555555555556</v>
@@ -42999,7 +42999,7 @@
         <v>-2.404488928814141</v>
       </c>
       <c r="H553" t="n">
-        <v>406.5707952146441</v>
+        <v>406.5707642578344</v>
       </c>
       <c r="I553" t="n">
         <v>255.5</v>
@@ -43008,7 +43008,7 @@
         <v>5.283757338551864</v>
       </c>
       <c r="K553" t="n">
-        <v>51.14155955934725</v>
+        <v>51.14154805123956</v>
       </c>
       <c r="L553" t="n">
         <v>12.36111111111111</v>
@@ -43458,7 +43458,7 @@
         <v>194.3287507629394</v>
       </c>
       <c r="G559" t="n">
-        <v>-3.726062648509398</v>
+        <v>-3.727183490370556</v>
       </c>
       <c r="H559" t="n">
         <v>322.394908081455</v>
@@ -43615,7 +43615,7 @@
         <v>-0.8873826761097159</v>
       </c>
       <c r="H561" t="n">
-        <v>828.2152046613147</v>
+        <v>828.2152668923007</v>
       </c>
       <c r="I561" t="n">
         <v>406.117116732523</v>
@@ -43624,7 +43624,7 @@
         <v>14.0065219917685</v>
       </c>
       <c r="K561" t="n">
-        <v>78.88017379294054</v>
+        <v>78.88018723375826</v>
       </c>
       <c r="L561" t="n">
         <v>6.805555555555555</v>
@@ -43923,7 +43923,7 @@
         <v>-1.9712649823863</v>
       </c>
       <c r="H565" t="n">
-        <v>546.5890454582147</v>
+        <v>546.5889842244101</v>
       </c>
       <c r="I565" t="n">
         <v>308.2000122070312</v>
@@ -43932,7 +43932,7 @@
         <v>0.7462646664088135</v>
       </c>
       <c r="K565" t="n">
-        <v>76.0351193102141</v>
+        <v>76.03509958918198</v>
       </c>
       <c r="L565" t="n">
         <v>4.444444444444445</v>
@@ -45543,10 +45543,10 @@
         <v>962.6932158005569</v>
       </c>
       <c r="I586" t="n">
-        <v>726.0613673587077</v>
+        <v>726.0614279588375</v>
       </c>
       <c r="J586" t="n">
-        <v>3.744674191962605</v>
+        <v>3.744665532997282</v>
       </c>
       <c r="K586" t="n">
         <v>27.80527259217482</v>
@@ -48235,7 +48235,7 @@
         <v>-2.342743021714566</v>
       </c>
       <c r="H621" t="n">
-        <v>239.2186883393384</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I621" t="n">
         <v>156.7443123050878</v>
@@ -48244,7 +48244,7 @@
         <v>10.78551517613684</v>
       </c>
       <c r="K621" t="n">
-        <v>37.75911128562471</v>
+        <v>37.75910239334252</v>
       </c>
       <c r="L621" t="n">
         <v>21.25</v>
@@ -48466,7 +48466,7 @@
         <v>-1.469371907015438</v>
       </c>
       <c r="H624" t="n">
-        <v>9653.121370296873</v>
+        <v>9653.120359649309</v>
       </c>
       <c r="I624" t="n">
         <v>6922</v>
@@ -48475,7 +48475,7 @@
         <v>2.167003756139851</v>
       </c>
       <c r="K624" t="n">
-        <v>36.49775693293089</v>
+        <v>36.49774264209995</v>
       </c>
       <c r="L624" t="n">
         <v>20.83333333333334</v>
@@ -48694,7 +48694,7 @@
         <v>229.043649520874</v>
       </c>
       <c r="G627" t="n">
-        <v>-2.329675674747778</v>
+        <v>-2.329384130519763</v>
       </c>
       <c r="H627" t="n">
         <v>285.8408427878384</v>
@@ -48851,7 +48851,7 @@
         <v>-2.337309146872313</v>
       </c>
       <c r="H629" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I629" t="n">
         <v>17.51000022888184</v>
@@ -48860,7 +48860,7 @@
         <v>1.313532491318625</v>
       </c>
       <c r="K629" t="n">
-        <v>34.35886446704277</v>
+        <v>34.35885319283845</v>
       </c>
       <c r="L629" t="n">
         <v>18.75</v>
@@ -49852,7 +49852,7 @@
         <v>-2.443351866282273</v>
       </c>
       <c r="H642" t="n">
-        <v>154.1041427094461</v>
+        <v>154.1041584954392</v>
       </c>
       <c r="I642" t="n">
         <v>104.7068431385872</v>
@@ -49861,7 +49861,7 @@
         <v>3.699050201848864</v>
       </c>
       <c r="K642" t="n">
-        <v>41.92681903728905</v>
+        <v>41.92683357587146</v>
       </c>
       <c r="L642" t="n">
         <v>15.13888888888889</v>
@@ -50853,7 +50853,7 @@
         <v>-3.539714089615098</v>
       </c>
       <c r="H655" t="n">
-        <v>1255.178308316206</v>
+        <v>1255.178432949836</v>
       </c>
       <c r="I655" t="n">
         <v>855.1500244140625</v>
@@ -50862,7 +50862,7 @@
         <v>2.905919999588891</v>
       </c>
       <c r="K655" t="n">
-        <v>42.63389867229614</v>
+        <v>42.63391283520865</v>
       </c>
       <c r="L655" t="n">
         <v>12.5</v>
@@ -51546,7 +51546,7 @@
         <v>-3.186612091689878</v>
       </c>
       <c r="H664" t="n">
-        <v>396.5816020628056</v>
+        <v>396.5816333492734</v>
       </c>
       <c r="I664" t="n">
         <v>243.9284560598348</v>
@@ -51555,7 +51555,7 @@
         <v>6.650121145632348</v>
       </c>
       <c r="K664" t="n">
-        <v>52.4434408484393</v>
+        <v>52.44345287475816</v>
       </c>
       <c r="L664" t="n">
         <v>10.55555555555556</v>
@@ -51700,7 +51700,7 @@
         <v>-3.074502430360115</v>
       </c>
       <c r="H666" t="n">
-        <v>263.220498300555</v>
+        <v>263.2205288662585</v>
       </c>
       <c r="I666" t="n">
         <v>161.6600036621094</v>
@@ -51709,7 +51709,7 @@
         <v>1.459854359080848</v>
       </c>
       <c r="K666" t="n">
-        <v>60.48072884043321</v>
+        <v>60.48074747578418</v>
       </c>
       <c r="L666" t="n">
         <v>10.27777777777778</v>
@@ -51777,7 +51777,7 @@
         <v>-1.259978388112681</v>
       </c>
       <c r="H667" t="n">
-        <v>3469.396141243416</v>
+        <v>3469.395895156339</v>
       </c>
       <c r="I667" t="n">
         <v>1805.687062514093</v>
@@ -51786,7 +51786,7 @@
         <v>9.121899653566556</v>
       </c>
       <c r="K667" t="n">
-        <v>76.07572565246539</v>
+        <v>76.07571316327164</v>
       </c>
       <c r="L667" t="n">
         <v>10</v>
@@ -54700,7 +54700,7 @@
         <v>776.7295007324219</v>
       </c>
       <c r="G705" t="n">
-        <v>-4.007803065774351</v>
+        <v>-4.006705721180515</v>
       </c>
       <c r="H705" t="n">
         <v>1235.294421692934</v>

--- a/output/minervini_4h.xlsx
+++ b/output/minervini_4h.xlsx
@@ -4730,7 +4730,7 @@
         <v>0.7475166936984579</v>
       </c>
       <c r="H56" t="n">
-        <v>1278.952852189353</v>
+        <v>1278.952725191461</v>
       </c>
       <c r="I56" t="n">
         <v>865.2617122743181</v>
@@ -4739,7 +4739,7 @@
         <v>41.58721670068974</v>
       </c>
       <c r="K56" t="n">
-        <v>4.39579443936069</v>
+        <v>4.395784073031805</v>
       </c>
       <c r="L56" t="n">
         <v>72.29916897506925</v>
@@ -6427,10 +6427,10 @@
         <v>8949.5</v>
       </c>
       <c r="I78" t="n">
-        <v>4504.255320019595</v>
+        <v>4504.255799235611</v>
       </c>
       <c r="J78" t="n">
-        <v>80.64029283234777</v>
+        <v>80.64027361369652</v>
       </c>
       <c r="K78" t="n">
         <v>9.992011307073057</v>
@@ -13123,7 +13123,7 @@
         <v>1.77111441026705</v>
       </c>
       <c r="H165" t="n">
-        <v>2256.187656125729</v>
+        <v>2256.187906504501</v>
       </c>
       <c r="I165" t="n">
         <v>1345.285007075603</v>
@@ -13132,7 +13132,7 @@
         <v>45.86500544548524</v>
       </c>
       <c r="K165" t="n">
-        <v>14.97669061737585</v>
+        <v>14.97670337682986</v>
       </c>
       <c r="L165" t="n">
         <v>61.91135734072022</v>
@@ -15741,7 +15741,7 @@
         <v>1.251003733641443</v>
       </c>
       <c r="H199" t="n">
-        <v>5005.771184298104</v>
+        <v>5005.771680286142</v>
       </c>
       <c r="I199" t="n">
         <v>3669.905008549105</v>
@@ -15750,7 +15750,7 @@
         <v>20.67342580638332</v>
       </c>
       <c r="K199" t="n">
-        <v>13.03281113477171</v>
+        <v>13.03282233442908</v>
       </c>
       <c r="L199" t="n">
         <v>66.06648199445983</v>
@@ -17438,10 +17438,10 @@
         <v>2295</v>
       </c>
       <c r="I221" t="n">
-        <v>1174.489600842614</v>
+        <v>1174.48971989473</v>
       </c>
       <c r="J221" t="n">
-        <v>59.6438145263116</v>
+        <v>59.64379834402105</v>
       </c>
       <c r="K221" t="n">
         <v>22.4</v>
@@ -24984,10 +24984,10 @@
         <v>2046.900024414062</v>
       </c>
       <c r="I319" t="n">
-        <v>1569.365993709292</v>
+        <v>1569.36587206911</v>
       </c>
       <c r="J319" t="n">
-        <v>14.75971871565962</v>
+        <v>14.7597276105855</v>
       </c>
       <c r="K319" t="n">
         <v>13.65352717457315</v>
@@ -25369,10 +25369,10 @@
         <v>489.5369231157038</v>
       </c>
       <c r="I324" t="n">
-        <v>331.4688100886702</v>
+        <v>331.4688402352409</v>
       </c>
       <c r="J324" t="n">
-        <v>20.4185678253435</v>
+        <v>20.41855687346379</v>
       </c>
       <c r="K324" t="n">
         <v>22.64485296288401</v>
@@ -26447,10 +26447,10 @@
         <v>43614.20556091995</v>
       </c>
       <c r="I338" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J338" t="n">
-        <v>24.16480247955331</v>
+        <v>24.16481058574358</v>
       </c>
       <c r="K338" t="n">
         <v>18.96946415962888</v>
@@ -27137,7 +27137,7 @@
         <v>-1.307795778998577</v>
       </c>
       <c r="H347" t="n">
-        <v>252.6160882566492</v>
+        <v>252.6161043110497</v>
       </c>
       <c r="I347" t="n">
         <v>171.6534204603822</v>
@@ -27146,7 +27146,7 @@
         <v>23.50467554413214</v>
       </c>
       <c r="K347" t="n">
-        <v>19.15853219653263</v>
+        <v>19.15853976936308</v>
       </c>
       <c r="L347" t="n">
         <v>40.85872576177285</v>
@@ -28372,10 +28372,10 @@
         <v>1093.53919041171</v>
       </c>
       <c r="I363" t="n">
-        <v>491.2850813456647</v>
+        <v>491.2850236715819</v>
       </c>
       <c r="J363" t="n">
-        <v>38.80942819169712</v>
+        <v>38.80944448713881</v>
       </c>
       <c r="K363" t="n">
         <v>60.35474313910942</v>
@@ -30217,7 +30217,7 @@
         <v>-1.00086154947302</v>
       </c>
       <c r="H387" t="n">
-        <v>1300.436795781491</v>
+        <v>1300.436668328248</v>
       </c>
       <c r="I387" t="n">
         <v>885.652283987356</v>
@@ -30226,7 +30226,7 @@
         <v>18.03729785548514</v>
       </c>
       <c r="K387" t="n">
-        <v>24.39609387902726</v>
+        <v>24.39608168721163</v>
       </c>
       <c r="L387" t="n">
         <v>44.73684210526316</v>
@@ -31603,7 +31603,7 @@
         <v>-1.228218510676249</v>
       </c>
       <c r="H405" t="n">
-        <v>547.7380341214969</v>
+        <v>547.7379722645398</v>
       </c>
       <c r="I405" t="n">
         <v>419.3328127807616</v>
@@ -31612,7 +31612,7 @@
         <v>5.405536253870347</v>
       </c>
       <c r="K405" t="n">
-        <v>23.92263215418482</v>
+        <v>23.92261815939816</v>
       </c>
       <c r="L405" t="n">
         <v>35.73407202216066</v>
@@ -34686,10 +34686,10 @@
         <v>2765.379504159864</v>
       </c>
       <c r="I445" t="n">
-        <v>1963.170239604111</v>
+        <v>1963.170361427068</v>
       </c>
       <c r="J445" t="n">
-        <v>6.129359439564164</v>
+        <v>6.129352853792192</v>
       </c>
       <c r="K445" t="n">
         <v>32.72759799183411</v>
@@ -36916,7 +36916,7 @@
         <v>-2.298798488095855</v>
       </c>
       <c r="H474" t="n">
-        <v>308.0746526166167</v>
+        <v>308.0746845932235</v>
       </c>
       <c r="I474" t="n">
         <v>185.2067002350832</v>
@@ -36925,7 +36925,7 @@
         <v>19.32613653797855</v>
       </c>
       <c r="K474" t="n">
-        <v>39.40029530163653</v>
+        <v>39.40030977068935</v>
       </c>
       <c r="L474" t="n">
         <v>30.05540166204986</v>
@@ -38148,7 +38148,7 @@
         <v>-1.08559434269031</v>
       </c>
       <c r="H490" t="n">
-        <v>2339.801318384509</v>
+        <v>2339.80156593166</v>
       </c>
       <c r="I490" t="n">
         <v>1322.972836511248</v>
@@ -38157,7 +38157,7 @@
         <v>17.38714183243149</v>
       </c>
       <c r="K490" t="n">
-        <v>50.66331734607268</v>
+        <v>50.66333328600516</v>
       </c>
       <c r="L490" t="n">
         <v>24.2382271468144</v>
@@ -38995,7 +38995,7 @@
         <v>-4.771807959862818</v>
       </c>
       <c r="H501" t="n">
-        <v>758.5896367271307</v>
+        <v>758.589574672296</v>
       </c>
       <c r="I501" t="n">
         <v>400.6499938964844</v>
@@ -39004,7 +39004,7 @@
         <v>17.73368760587177</v>
       </c>
       <c r="K501" t="n">
-        <v>60.82035554287464</v>
+        <v>60.82034238730263</v>
       </c>
       <c r="L501" t="n">
         <v>19.39058171745152</v>
@@ -39534,7 +39534,7 @@
         <v>-2.457765333832462</v>
       </c>
       <c r="H508" t="n">
-        <v>1507.849092404508</v>
+        <v>1507.849216441457</v>
       </c>
       <c r="I508" t="n">
         <v>1015.099975585938</v>
@@ -39543,7 +39543,7 @@
         <v>2.452962763563238</v>
       </c>
       <c r="K508" t="n">
-        <v>44.98548965427958</v>
+        <v>44.9855015809093</v>
       </c>
       <c r="L508" t="n">
         <v>14.12742382271468</v>
@@ -40535,7 +40535,7 @@
         <v>-2.372580495459409</v>
       </c>
       <c r="H521" t="n">
-        <v>1181.515387363553</v>
+        <v>1181.515511428121</v>
       </c>
       <c r="I521" t="n">
         <v>577.3964738257137</v>
@@ -40544,7 +40544,7 @@
         <v>6.166218151348324</v>
       </c>
       <c r="K521" t="n">
-        <v>92.74313007562034</v>
+        <v>92.74315031453844</v>
       </c>
       <c r="L521" t="n">
         <v>8.171745152354571</v>
@@ -42925,10 +42925,10 @@
         <v>409.9712889887167</v>
       </c>
       <c r="I552" t="n">
-        <v>309.8384816659088</v>
+        <v>309.838511773213</v>
       </c>
       <c r="J552" t="n">
-        <v>1.698150729798686</v>
+        <v>1.698140847692242</v>
       </c>
       <c r="K552" t="n">
         <v>30.10830880594595</v>
@@ -43002,10 +43002,10 @@
         <v>1224.741935222577</v>
       </c>
       <c r="I553" t="n">
-        <v>787.9767964287304</v>
+        <v>787.976735462851</v>
       </c>
       <c r="J553" t="n">
-        <v>3.937070699527334</v>
+        <v>3.937078741154232</v>
       </c>
       <c r="K553" t="n">
         <v>49.54113983181652</v>
@@ -45848,7 +45848,7 @@
         <v>-1.243050503642118</v>
       </c>
       <c r="H590" t="n">
-        <v>509.5710734571873</v>
+        <v>509.5710426414886</v>
       </c>
       <c r="I590" t="n">
         <v>394.4382907843191</v>
@@ -45857,7 +45857,7 @@
         <v>1.169180862101271</v>
       </c>
       <c r="K590" t="n">
-        <v>27.69605038092571</v>
+        <v>27.69604265866043</v>
       </c>
       <c r="L590" t="n">
         <v>26.0387811634349</v>
@@ -46541,7 +46541,7 @@
         <v>-2.809267312629482</v>
       </c>
       <c r="H599" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I599" t="n">
         <v>16.75</v>
@@ -46550,7 +46550,7 @@
         <v>1.49253731343284</v>
       </c>
       <c r="K599" t="n">
-        <v>40.20742499370795</v>
+        <v>40.2074132287443</v>
       </c>
       <c r="L599" t="n">
         <v>23.54570637119114</v>
@@ -47311,7 +47311,7 @@
         <v>-2.105672528959868</v>
       </c>
       <c r="H609" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I609" t="n">
         <v>104.1800003051758</v>
@@ -47320,7 +47320,7 @@
         <v>1.727781768559256</v>
       </c>
       <c r="K609" t="n">
-        <v>47.10318528194084</v>
+        <v>47.10320195970523</v>
       </c>
       <c r="L609" t="n">
         <v>21.32963988919667</v>
@@ -48312,7 +48312,7 @@
         <v>-2.434827827907715</v>
       </c>
       <c r="H622" t="n">
-        <v>3287.161645949698</v>
+        <v>3287.161392369851</v>
       </c>
       <c r="I622" t="n">
         <v>1966.020518717901</v>
@@ -48321,7 +48321,7 @@
         <v>5.543150757814441</v>
       </c>
       <c r="K622" t="n">
-        <v>58.41742872046736</v>
+        <v>58.41741649975183</v>
       </c>
       <c r="L622" t="n">
         <v>18.5595567867036</v>
@@ -50237,7 +50237,7 @@
         <v>-3.407045752144122</v>
       </c>
       <c r="H647" t="n">
-        <v>239.2187037807859</v>
+        <v>239.2186883393384</v>
       </c>
       <c r="I647" t="n">
         <v>156.7443123050878</v>
@@ -50246,7 +50246,7 @@
         <v>3.059556618367543</v>
       </c>
       <c r="K647" t="n">
-        <v>48.08636481559228</v>
+        <v>48.08635525669163</v>
       </c>
       <c r="L647" t="n">
         <v>14.26592797783933</v>
@@ -50622,7 +50622,7 @@
         <v>-3.839819480592788</v>
       </c>
       <c r="H652" t="n">
-        <v>396.5816646357411</v>
+        <v>396.5816333492734</v>
       </c>
       <c r="I652" t="n">
         <v>243.9284560598348</v>
@@ -50631,7 +50631,7 @@
         <v>5.563739532232415</v>
       </c>
       <c r="K652" t="n">
-        <v>54.01229694591887</v>
+        <v>54.01228479583433</v>
       </c>
       <c r="L652" t="n">
         <v>12.8808864265928</v>
@@ -50930,7 +50930,7 @@
         <v>-3.540814181367447</v>
       </c>
       <c r="H656" t="n">
-        <v>1255.178432949836</v>
+        <v>1255.178308316206</v>
       </c>
       <c r="I656" t="n">
         <v>838</v>
@@ -50939,7 +50939,7 @@
         <v>0.2386634844868674</v>
       </c>
       <c r="K656" t="n">
-        <v>49.42600392259955</v>
+        <v>49.42598908526264</v>
       </c>
       <c r="L656" t="n">
         <v>11.91135734072022</v>
@@ -51392,7 +51392,7 @@
         <v>-3.017161457530726</v>
       </c>
       <c r="H662" t="n">
-        <v>725.6811213920008</v>
+        <v>725.6811828531856</v>
       </c>
       <c r="I662" t="n">
         <v>446.0256812201048</v>
@@ -51401,7 +51401,7 @@
         <v>1.810282506900385</v>
       </c>
       <c r="K662" t="n">
-        <v>59.80645488619001</v>
+        <v>59.80646842091453</v>
       </c>
       <c r="L662" t="n">
         <v>10.94182825484764</v>
